--- a/New_Pv_Data3.xlsx
+++ b/New_Pv_Data3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISD\Python_ali\fault_detection\jupyter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB55F98-B12B-42EF-BBAC-AB1041203674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0321623-4E44-4DF9-A03F-D80595F366F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="13">
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>5,7</t>
+  </si>
+  <si>
+    <t>3,6</t>
+  </si>
+  <si>
+    <t>7,4</t>
+  </si>
+  <si>
+    <t>8,1</t>
+  </si>
+  <si>
+    <t>5,2</t>
+  </si>
+  <si>
+    <t>4,8</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>5,6</t>
+  </si>
+  <si>
+    <t>7,8</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>6,7</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59,12 +99,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8879,8 +8922,8 @@
       <c r="P161" s="1">
         <v>1.6819999999999999</v>
       </c>
-      <c r="Q161" s="2">
-        <v>9</v>
+      <c r="Q161" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -8932,8 +8975,8 @@
       <c r="P162" s="1">
         <v>1.627</v>
       </c>
-      <c r="Q162" s="2">
-        <v>9</v>
+      <c r="Q162" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -8985,8 +9028,8 @@
       <c r="P163" s="1">
         <v>1.609</v>
       </c>
-      <c r="Q163" s="2">
-        <v>9</v>
+      <c r="Q163" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -9038,8 +9081,8 @@
       <c r="P164" s="1">
         <v>1.7110000000000001</v>
       </c>
-      <c r="Q164" s="2">
-        <v>9</v>
+      <c r="Q164" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -9091,8 +9134,8 @@
       <c r="P165" s="1">
         <v>1.6850000000000001</v>
       </c>
-      <c r="Q165" s="2">
-        <v>9</v>
+      <c r="Q165" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -9144,8 +9187,8 @@
       <c r="P166" s="1">
         <v>1.653</v>
       </c>
-      <c r="Q166" s="2">
-        <v>9</v>
+      <c r="Q166" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -9197,8 +9240,8 @@
       <c r="P167" s="1">
         <v>1.958</v>
       </c>
-      <c r="Q167" s="2">
-        <v>9</v>
+      <c r="Q167" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -9250,8 +9293,8 @@
       <c r="P168" s="1">
         <v>1.9219999999999999</v>
       </c>
-      <c r="Q168" s="2">
-        <v>9</v>
+      <c r="Q168" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -9303,8 +9346,8 @@
       <c r="P169" s="1">
         <v>1.891</v>
       </c>
-      <c r="Q169" s="2">
-        <v>9</v>
+      <c r="Q169" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -9356,8 +9399,8 @@
       <c r="P170" s="1">
         <v>2.2189999999999999</v>
       </c>
-      <c r="Q170" s="2">
-        <v>9</v>
+      <c r="Q170" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -9409,8 +9452,8 @@
       <c r="P171" s="1">
         <v>2.1850000000000001</v>
       </c>
-      <c r="Q171" s="2">
-        <v>9</v>
+      <c r="Q171" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -9462,8 +9505,8 @@
       <c r="P172" s="1">
         <v>2.1509999999999998</v>
       </c>
-      <c r="Q172" s="2">
-        <v>9</v>
+      <c r="Q172" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -9515,8 +9558,8 @@
       <c r="P173" s="1">
         <v>2.5449999999999999</v>
       </c>
-      <c r="Q173" s="2">
-        <v>9</v>
+      <c r="Q173" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -9568,8 +9611,8 @@
       <c r="P174" s="1">
         <v>2.472</v>
       </c>
-      <c r="Q174" s="2">
-        <v>9</v>
+      <c r="Q174" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -9621,8 +9664,8 @@
       <c r="P175" s="1">
         <v>2.4489999999999998</v>
       </c>
-      <c r="Q175" s="2">
-        <v>9</v>
+      <c r="Q175" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -9674,8 +9717,8 @@
       <c r="P176" s="1">
         <v>2.8279999999999998</v>
       </c>
-      <c r="Q176" s="2">
-        <v>9</v>
+      <c r="Q176" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -9727,8 +9770,8 @@
       <c r="P177" s="1">
         <v>2.7970000000000002</v>
       </c>
-      <c r="Q177" s="2">
-        <v>9</v>
+      <c r="Q177" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -9780,8 +9823,8 @@
       <c r="P178" s="1">
         <v>2.7709999999999999</v>
       </c>
-      <c r="Q178" s="2">
-        <v>9</v>
+      <c r="Q178" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -9833,8 +9876,8 @@
       <c r="P179" s="1">
         <v>3.173</v>
       </c>
-      <c r="Q179" s="2">
-        <v>9</v>
+      <c r="Q179" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -9886,8 +9929,8 @@
       <c r="P180" s="1">
         <v>3.1480000000000001</v>
       </c>
-      <c r="Q180" s="2">
-        <v>9</v>
+      <c r="Q180" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -9939,8 +9982,8 @@
       <c r="P181" s="1">
         <v>3.1150000000000002</v>
       </c>
-      <c r="Q181" s="2">
-        <v>10</v>
+      <c r="Q181" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -9992,8 +10035,8 @@
       <c r="P182" s="1">
         <v>3.5430000000000001</v>
       </c>
-      <c r="Q182" s="2">
-        <v>10</v>
+      <c r="Q182" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -10045,8 +10088,8 @@
       <c r="P183" s="1">
         <v>3.516</v>
       </c>
-      <c r="Q183" s="2">
-        <v>10</v>
+      <c r="Q183" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -10098,8 +10141,8 @@
       <c r="P184" s="1">
         <v>3.7240000000000002</v>
       </c>
-      <c r="Q184" s="2">
-        <v>10</v>
+      <c r="Q184" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -10151,8 +10194,8 @@
       <c r="P185" s="1">
         <v>3.6960000000000002</v>
       </c>
-      <c r="Q185" s="2">
-        <v>10</v>
+      <c r="Q185" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -10204,8 +10247,8 @@
       <c r="P186" s="1">
         <v>3.681</v>
       </c>
-      <c r="Q186" s="2">
-        <v>10</v>
+      <c r="Q186" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -10257,8 +10300,8 @@
       <c r="P187" s="1">
         <v>3.891</v>
       </c>
-      <c r="Q187" s="2">
-        <v>10</v>
+      <c r="Q187" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -10310,8 +10353,8 @@
       <c r="P188" s="1">
         <v>3.8639999999999999</v>
       </c>
-      <c r="Q188" s="2">
-        <v>10</v>
+      <c r="Q188" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -10363,8 +10406,8 @@
       <c r="P189" s="1">
         <v>3.83</v>
       </c>
-      <c r="Q189" s="2">
-        <v>10</v>
+      <c r="Q189" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -10416,8 +10459,8 @@
       <c r="P190" s="1">
         <v>4.0510000000000002</v>
       </c>
-      <c r="Q190" s="2">
-        <v>10</v>
+      <c r="Q190" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -10469,8 +10512,8 @@
       <c r="P191" s="1">
         <v>4.0250000000000004</v>
       </c>
-      <c r="Q191" s="2">
-        <v>10</v>
+      <c r="Q191" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -10522,8 +10565,8 @@
       <c r="P192" s="1">
         <v>3.9990000000000001</v>
       </c>
-      <c r="Q192" s="2">
-        <v>10</v>
+      <c r="Q192" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -10575,8 +10618,8 @@
       <c r="P193" s="1">
         <v>4.2249999999999996</v>
       </c>
-      <c r="Q193" s="2">
-        <v>10</v>
+      <c r="Q193" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -10628,8 +10671,8 @@
       <c r="P194" s="1">
         <v>4.1989999999999998</v>
       </c>
-      <c r="Q194" s="2">
-        <v>10</v>
+      <c r="Q194" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -10681,8 +10724,8 @@
       <c r="P195" s="1">
         <v>4.1740000000000004</v>
       </c>
-      <c r="Q195" s="2">
-        <v>10</v>
+      <c r="Q195" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -10734,8 +10777,8 @@
       <c r="P196" s="1">
         <v>4.4050000000000002</v>
       </c>
-      <c r="Q196" s="2">
-        <v>10</v>
+      <c r="Q196" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -10787,8 +10830,8 @@
       <c r="P197" s="1">
         <v>4.3810000000000002</v>
       </c>
-      <c r="Q197" s="2">
-        <v>10</v>
+      <c r="Q197" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -10840,8 +10883,8 @@
       <c r="P198" s="1">
         <v>4.3559999999999999</v>
       </c>
-      <c r="Q198" s="2">
-        <v>10</v>
+      <c r="Q198" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -10893,8 +10936,8 @@
       <c r="P199" s="1">
         <v>4.5919999999999996</v>
       </c>
-      <c r="Q199" s="2">
-        <v>10</v>
+      <c r="Q199" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -10946,8 +10989,8 @@
       <c r="P200" s="1">
         <v>4.569</v>
       </c>
-      <c r="Q200" s="2">
-        <v>10</v>
+      <c r="Q200" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -10999,8 +11042,8 @@
       <c r="P201" s="1">
         <v>4.5419999999999998</v>
       </c>
-      <c r="Q201" s="2">
-        <v>11</v>
+      <c r="Q201" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -11052,8 +11095,8 @@
       <c r="P202" s="1">
         <v>4.7859999999999996</v>
       </c>
-      <c r="Q202" s="2">
-        <v>11</v>
+      <c r="Q202" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -11105,8 +11148,8 @@
       <c r="P203" s="1">
         <v>4.7629999999999999</v>
       </c>
-      <c r="Q203" s="2">
-        <v>11</v>
+      <c r="Q203" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -11158,8 +11201,8 @@
       <c r="P204" s="1">
         <v>4.74</v>
       </c>
-      <c r="Q204" s="2">
-        <v>11</v>
+      <c r="Q204" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -11211,8 +11254,8 @@
       <c r="P205" s="1">
         <v>4.9880000000000004</v>
       </c>
-      <c r="Q205" s="2">
-        <v>11</v>
+      <c r="Q205" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -11264,8 +11307,8 @@
       <c r="P206" s="1">
         <v>4.9630000000000001</v>
       </c>
-      <c r="Q206" s="2">
-        <v>11</v>
+      <c r="Q206" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -11317,8 +11360,8 @@
       <c r="P207" s="1">
         <v>4.9400000000000004</v>
       </c>
-      <c r="Q207" s="2">
-        <v>11</v>
+      <c r="Q207" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -11370,8 +11413,8 @@
       <c r="P208" s="1">
         <v>5.1909999999999998</v>
       </c>
-      <c r="Q208" s="2">
-        <v>11</v>
+      <c r="Q208" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -11423,8 +11466,8 @@
       <c r="P209" s="1">
         <v>5.1680000000000001</v>
       </c>
-      <c r="Q209" s="2">
-        <v>11</v>
+      <c r="Q209" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
@@ -11476,8 +11519,8 @@
       <c r="P210" s="1">
         <v>5.1470000000000002</v>
       </c>
-      <c r="Q210" s="2">
-        <v>11</v>
+      <c r="Q210" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
@@ -11529,8 +11572,8 @@
       <c r="P211" s="1">
         <v>5.4009999999999998</v>
       </c>
-      <c r="Q211" s="2">
-        <v>11</v>
+      <c r="Q211" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
@@ -11582,8 +11625,8 @@
       <c r="P212" s="1">
         <v>5.38</v>
       </c>
-      <c r="Q212" s="2">
-        <v>11</v>
+      <c r="Q212" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
@@ -11635,8 +11678,8 @@
       <c r="P213" s="1">
         <v>5.359</v>
       </c>
-      <c r="Q213" s="2">
-        <v>11</v>
+      <c r="Q213" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
@@ -11688,8 +11731,8 @@
       <c r="P214" s="1">
         <v>5.617</v>
       </c>
-      <c r="Q214" s="2">
-        <v>11</v>
+      <c r="Q214" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -11741,8 +11784,8 @@
       <c r="P215" s="1">
         <v>5.5960000000000001</v>
       </c>
-      <c r="Q215" s="2">
-        <v>11</v>
+      <c r="Q215" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
@@ -11794,8 +11837,8 @@
       <c r="P216" s="1">
         <v>5.5759999999999996</v>
       </c>
-      <c r="Q216" s="2">
-        <v>11</v>
+      <c r="Q216" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
@@ -11847,8 +11890,8 @@
       <c r="P217" s="1">
         <v>5.8380000000000001</v>
       </c>
-      <c r="Q217" s="2">
-        <v>11</v>
+      <c r="Q217" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
@@ -11900,8 +11943,8 @@
       <c r="P218" s="1">
         <v>5.8170000000000002</v>
       </c>
-      <c r="Q218" s="2">
-        <v>11</v>
+      <c r="Q218" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="219" spans="1:17" x14ac:dyDescent="0.25">
@@ -11953,8 +11996,8 @@
       <c r="P219" s="1">
         <v>5.7960000000000003</v>
       </c>
-      <c r="Q219" s="2">
-        <v>11</v>
+      <c r="Q219" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
@@ -12006,8 +12049,8 @@
       <c r="P220" s="1">
         <v>6.0640000000000001</v>
       </c>
-      <c r="Q220" s="2">
-        <v>11</v>
+      <c r="Q220" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
@@ -12059,8 +12102,8 @@
       <c r="P221" s="1">
         <v>4.4669999999999996</v>
       </c>
-      <c r="Q221" s="2">
-        <v>12</v>
+      <c r="Q221" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
@@ -12112,8 +12155,8 @@
       <c r="P222" s="1">
         <v>4.5179999999999998</v>
       </c>
-      <c r="Q222" s="2">
-        <v>12</v>
+      <c r="Q222" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
@@ -12165,8 +12208,8 @@
       <c r="P223" s="1">
         <v>4.5780000000000003</v>
       </c>
-      <c r="Q223" s="2">
-        <v>12</v>
+      <c r="Q223" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
@@ -12218,8 +12261,8 @@
       <c r="P224" s="1">
         <v>4.641</v>
       </c>
-      <c r="Q224" s="2">
-        <v>12</v>
+      <c r="Q224" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.25">
@@ -12271,8 +12314,8 @@
       <c r="P225" s="1">
         <v>4.7009999999999996</v>
       </c>
-      <c r="Q225" s="2">
-        <v>12</v>
+      <c r="Q225" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="226" spans="1:17" x14ac:dyDescent="0.25">
@@ -12324,8 +12367,8 @@
       <c r="P226" s="1">
         <v>4.7610000000000001</v>
       </c>
-      <c r="Q226" s="2">
-        <v>12</v>
+      <c r="Q226" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
@@ -12377,8 +12420,8 @@
       <c r="P227" s="1">
         <v>4.8209999999999997</v>
       </c>
-      <c r="Q227" s="2">
-        <v>12</v>
+      <c r="Q227" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
@@ -12430,8 +12473,8 @@
       <c r="P228" s="1">
         <v>4.8840000000000003</v>
       </c>
-      <c r="Q228" s="2">
-        <v>12</v>
+      <c r="Q228" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="229" spans="1:17" x14ac:dyDescent="0.25">
@@ -12483,8 +12526,8 @@
       <c r="P229" s="1">
         <v>4.952</v>
       </c>
-      <c r="Q229" s="2">
-        <v>12</v>
+      <c r="Q229" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.25">
@@ -12536,8 +12579,8 @@
       <c r="P230" s="1">
         <v>5.0039999999999996</v>
       </c>
-      <c r="Q230" s="2">
-        <v>12</v>
+      <c r="Q230" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.25">
@@ -12589,8 +12632,8 @@
       <c r="P231" s="1">
         <v>5.0640000000000001</v>
       </c>
-      <c r="Q231" s="2">
-        <v>12</v>
+      <c r="Q231" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="232" spans="1:17" x14ac:dyDescent="0.25">
@@ -12642,8 +12685,8 @@
       <c r="P232" s="1">
         <v>5.1269999999999998</v>
       </c>
-      <c r="Q232" s="2">
-        <v>12</v>
+      <c r="Q232" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.25">
@@ -12695,8 +12738,8 @@
       <c r="P233" s="1">
         <v>5.1870000000000003</v>
       </c>
-      <c r="Q233" s="2">
-        <v>12</v>
+      <c r="Q233" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:17" x14ac:dyDescent="0.25">
@@ -12748,8 +12791,8 @@
       <c r="P234" s="1">
         <v>5.2469999999999999</v>
       </c>
-      <c r="Q234" s="2">
-        <v>12</v>
+      <c r="Q234" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:17" x14ac:dyDescent="0.25">
@@ -12801,8 +12844,8 @@
       <c r="P235" s="1">
         <v>5.32</v>
       </c>
-      <c r="Q235" s="2">
-        <v>12</v>
+      <c r="Q235" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.25">
@@ -12854,8 +12897,8 @@
       <c r="P236" s="1">
         <v>5.37</v>
       </c>
-      <c r="Q236" s="2">
-        <v>12</v>
+      <c r="Q236" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:17" x14ac:dyDescent="0.25">
@@ -12907,8 +12950,8 @@
       <c r="P237" s="1">
         <v>5.43</v>
       </c>
-      <c r="Q237" s="2">
-        <v>12</v>
+      <c r="Q237" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:17" x14ac:dyDescent="0.25">
@@ -12960,8 +13003,8 @@
       <c r="P238" s="1">
         <v>5.4930000000000003</v>
       </c>
-      <c r="Q238" s="2">
-        <v>12</v>
+      <c r="Q238" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="239" spans="1:17" x14ac:dyDescent="0.25">
@@ -13013,8 +13056,8 @@
       <c r="P239" s="1">
         <v>5.5529999999999999</v>
       </c>
-      <c r="Q239" s="2">
-        <v>12</v>
+      <c r="Q239" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="240" spans="1:17" x14ac:dyDescent="0.25">
@@ -13066,8 +13109,8 @@
       <c r="P240" s="1">
         <v>5.1630000000000003</v>
       </c>
-      <c r="Q240" s="2">
-        <v>12</v>
+      <c r="Q240" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="241" spans="1:17" x14ac:dyDescent="0.25">
@@ -13119,8 +13162,8 @@
       <c r="P241" s="1">
         <v>5.6760000000000002</v>
       </c>
-      <c r="Q241" s="2">
-        <v>12</v>
+      <c r="Q241" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:17" x14ac:dyDescent="0.25">
@@ -13172,8 +13215,8 @@
       <c r="P242" s="1">
         <v>5.7359999999999998</v>
       </c>
-      <c r="Q242" s="2">
-        <v>12</v>
+      <c r="Q242" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:17" x14ac:dyDescent="0.25">
@@ -13225,8 +13268,8 @@
       <c r="P243" s="1">
         <v>5.7969999999999997</v>
       </c>
-      <c r="Q243" s="2">
-        <v>12</v>
+      <c r="Q243" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:17" x14ac:dyDescent="0.25">
@@ -13278,8 +13321,8 @@
       <c r="P244" s="1">
         <v>5.86</v>
       </c>
-      <c r="Q244" s="2">
-        <v>12</v>
+      <c r="Q244" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="245" spans="1:17" x14ac:dyDescent="0.25">
@@ -13331,8 +13374,8 @@
       <c r="P245" s="1">
         <v>5.92</v>
       </c>
-      <c r="Q245" s="2">
-        <v>12</v>
+      <c r="Q245" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="246" spans="1:17" x14ac:dyDescent="0.25">
@@ -13384,8 +13427,8 @@
       <c r="P246" s="1">
         <v>7.673</v>
       </c>
-      <c r="Q246" s="2">
-        <v>13</v>
+      <c r="Q246" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:17" x14ac:dyDescent="0.25">
@@ -13437,8 +13480,8 @@
       <c r="P247" s="1">
         <v>7.6559999999999997</v>
       </c>
-      <c r="Q247" s="2">
-        <v>13</v>
+      <c r="Q247" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:17" x14ac:dyDescent="0.25">
@@ -13490,8 +13533,8 @@
       <c r="P248" s="1">
         <v>7.95</v>
       </c>
-      <c r="Q248" s="2">
-        <v>13</v>
+      <c r="Q248" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:17" x14ac:dyDescent="0.25">
@@ -13543,8 +13586,8 @@
       <c r="P249" s="1">
         <v>7.9320000000000004</v>
       </c>
-      <c r="Q249" s="2">
-        <v>13</v>
+      <c r="Q249" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:17" x14ac:dyDescent="0.25">
@@ -13596,8 +13639,8 @@
       <c r="P250" s="1">
         <v>7.915</v>
       </c>
-      <c r="Q250" s="2">
-        <v>13</v>
+      <c r="Q250" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:17" x14ac:dyDescent="0.25">
@@ -13649,8 +13692,8 @@
       <c r="P251" s="1">
         <v>7.8979999999999997</v>
       </c>
-      <c r="Q251" s="2">
-        <v>13</v>
+      <c r="Q251" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:17" x14ac:dyDescent="0.25">
@@ -13702,8 +13745,8 @@
       <c r="P252" s="1">
         <v>8.1940000000000008</v>
       </c>
-      <c r="Q252" s="2">
-        <v>13</v>
+      <c r="Q252" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:17" x14ac:dyDescent="0.25">
@@ -13755,8 +13798,8 @@
       <c r="P253" s="1">
         <v>8.1760000000000002</v>
       </c>
-      <c r="Q253" s="2">
-        <v>13</v>
+      <c r="Q253" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:17" x14ac:dyDescent="0.25">
@@ -13808,8 +13851,8 @@
       <c r="P254" s="1">
         <v>8.1609999999999996</v>
       </c>
-      <c r="Q254" s="2">
-        <v>13</v>
+      <c r="Q254" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:17" x14ac:dyDescent="0.25">
@@ -13861,8 +13904,8 @@
       <c r="P255" s="1">
         <v>8.1449999999999996</v>
       </c>
-      <c r="Q255" s="2">
-        <v>13</v>
+      <c r="Q255" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:17" x14ac:dyDescent="0.25">
@@ -13914,8 +13957,8 @@
       <c r="P256" s="1">
         <v>8.4429999999999996</v>
       </c>
-      <c r="Q256" s="2">
-        <v>13</v>
+      <c r="Q256" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:17" x14ac:dyDescent="0.25">
@@ -13967,8 +14010,8 @@
       <c r="P257" s="1">
         <v>8.4260000000000002</v>
       </c>
-      <c r="Q257" s="2">
-        <v>13</v>
+      <c r="Q257" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:17" x14ac:dyDescent="0.25">
@@ -14020,8 +14063,8 @@
       <c r="P258" s="1">
         <v>8.4109999999999996</v>
       </c>
-      <c r="Q258" s="2">
-        <v>13</v>
+      <c r="Q258" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:17" x14ac:dyDescent="0.25">
@@ -14073,8 +14116,8 @@
       <c r="P259" s="1">
         <v>8.3949999999999996</v>
       </c>
-      <c r="Q259" s="2">
-        <v>13</v>
+      <c r="Q259" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:17" x14ac:dyDescent="0.25">
@@ -14126,8 +14169,8 @@
       <c r="P260" s="1">
         <v>8.6950000000000003</v>
       </c>
-      <c r="Q260" s="2">
-        <v>13</v>
+      <c r="Q260" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:17" x14ac:dyDescent="0.25">
@@ -14179,8 +14222,8 @@
       <c r="P261" s="1">
         <v>8.6790000000000003</v>
       </c>
-      <c r="Q261" s="2">
-        <v>13</v>
+      <c r="Q261" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:17" x14ac:dyDescent="0.25">
@@ -14232,8 +14275,8 @@
       <c r="P262" s="1">
         <v>8.6639999999999997</v>
       </c>
-      <c r="Q262" s="2">
-        <v>13</v>
+      <c r="Q262" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:17" x14ac:dyDescent="0.25">
@@ -14285,8 +14328,8 @@
       <c r="P263" s="1">
         <v>8.6460000000000008</v>
       </c>
-      <c r="Q263" s="2">
-        <v>13</v>
+      <c r="Q263" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:17" x14ac:dyDescent="0.25">
@@ -14338,8 +14381,8 @@
       <c r="P264" s="1">
         <v>8.6319999999999997</v>
       </c>
-      <c r="Q264" s="2">
-        <v>13</v>
+      <c r="Q264" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:17" x14ac:dyDescent="0.25">
@@ -14391,8 +14434,8 @@
       <c r="P265" s="1">
         <v>8.9359999999999999</v>
       </c>
-      <c r="Q265" s="2">
-        <v>13</v>
+      <c r="Q265" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="266" spans="1:17" x14ac:dyDescent="0.25">
@@ -14444,8 +14487,8 @@
       <c r="P266" s="1">
         <v>8.92</v>
       </c>
-      <c r="Q266" s="2">
-        <v>13</v>
+      <c r="Q266" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:17" x14ac:dyDescent="0.25">
@@ -14497,8 +14540,8 @@
       <c r="P267" s="1">
         <v>8.9039999999999999</v>
       </c>
-      <c r="Q267" s="2">
-        <v>13</v>
+      <c r="Q267" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:17" x14ac:dyDescent="0.25">
@@ -14550,8 +14593,8 @@
       <c r="P268" s="1">
         <v>9.2100000000000009</v>
       </c>
-      <c r="Q268" s="2">
-        <v>13</v>
+      <c r="Q268" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:17" x14ac:dyDescent="0.25">
@@ -14603,8 +14646,8 @@
       <c r="P269" s="1">
         <v>9.1950000000000003</v>
       </c>
-      <c r="Q269" s="2">
-        <v>13</v>
+      <c r="Q269" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:17" x14ac:dyDescent="0.25">
@@ -14656,8 +14699,8 @@
       <c r="P270" s="1">
         <v>9.18</v>
       </c>
-      <c r="Q270" s="2">
-        <v>14</v>
+      <c r="Q270" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="271" spans="1:17" x14ac:dyDescent="0.25">
@@ -14709,8 +14752,8 @@
       <c r="P271" s="1">
         <v>9.1649999999999991</v>
       </c>
-      <c r="Q271" s="2">
-        <v>14</v>
+      <c r="Q271" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="272" spans="1:17" x14ac:dyDescent="0.25">
@@ -14762,8 +14805,8 @@
       <c r="P272" s="1">
         <v>9.6359999999999992</v>
       </c>
-      <c r="Q272" s="2">
-        <v>14</v>
+      <c r="Q272" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="273" spans="1:17" x14ac:dyDescent="0.25">
@@ -14815,8 +14858,8 @@
       <c r="P273" s="1">
         <v>9.7799999999999994</v>
       </c>
-      <c r="Q273" s="2">
-        <v>14</v>
+      <c r="Q273" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="274" spans="1:17" x14ac:dyDescent="0.25">
@@ -14868,8 +14911,8 @@
       <c r="P274" s="2">
         <v>9.7669999999999995</v>
       </c>
-      <c r="Q274" s="2">
-        <v>14</v>
+      <c r="Q274" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="275" spans="1:17" x14ac:dyDescent="0.25">
@@ -14921,8 +14964,8 @@
       <c r="P275" s="2">
         <v>9.7520000000000007</v>
       </c>
-      <c r="Q275" s="2">
-        <v>14</v>
+      <c r="Q275" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="276" spans="1:17" x14ac:dyDescent="0.25">
@@ -14974,8 +15017,8 @@
       <c r="P276" s="2">
         <v>9.74</v>
       </c>
-      <c r="Q276" s="2">
-        <v>14</v>
+      <c r="Q276" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="277" spans="1:17" x14ac:dyDescent="0.25">
@@ -15027,8 +15070,8 @@
       <c r="P277" s="2">
         <v>9.7230000000000008</v>
       </c>
-      <c r="Q277" s="2">
-        <v>14</v>
+      <c r="Q277" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="278" spans="1:17" x14ac:dyDescent="0.25">
@@ -15080,8 +15123,8 @@
       <c r="P278" s="2">
         <v>9.7089999999999996</v>
       </c>
-      <c r="Q278" s="2">
-        <v>14</v>
+      <c r="Q278" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="279" spans="1:17" x14ac:dyDescent="0.25">
@@ -15133,8 +15176,8 @@
       <c r="P279" s="2">
         <v>9.6940000000000008</v>
       </c>
-      <c r="Q279" s="2">
-        <v>14</v>
+      <c r="Q279" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="280" spans="1:17" x14ac:dyDescent="0.25">
@@ -15186,8 +15229,8 @@
       <c r="P280" s="2">
         <v>9.68</v>
       </c>
-      <c r="Q280" s="2">
-        <v>14</v>
+      <c r="Q280" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="281" spans="1:17" x14ac:dyDescent="0.25">
@@ -15239,8 +15282,8 @@
       <c r="P281" s="2">
         <v>9.9909999999999997</v>
       </c>
-      <c r="Q281" s="2">
-        <v>14</v>
+      <c r="Q281" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="282" spans="1:17" x14ac:dyDescent="0.25">
@@ -15292,8 +15335,8 @@
       <c r="P282" s="2">
         <v>9.9770000000000003</v>
       </c>
-      <c r="Q282" s="2">
-        <v>14</v>
+      <c r="Q282" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="283" spans="1:17" x14ac:dyDescent="0.25">
@@ -15345,8 +15388,8 @@
       <c r="P283" s="2">
         <v>9.9629999999999992</v>
       </c>
-      <c r="Q283" s="2">
-        <v>14</v>
+      <c r="Q283" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="284" spans="1:17" x14ac:dyDescent="0.25">
@@ -15398,8 +15441,8 @@
       <c r="P284" s="2">
         <v>9.9489999999999998</v>
       </c>
-      <c r="Q284" s="2">
-        <v>14</v>
+      <c r="Q284" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="285" spans="1:17" x14ac:dyDescent="0.25">
@@ -15451,8 +15494,8 @@
       <c r="P285" s="2">
         <v>9.9350000000000005</v>
       </c>
-      <c r="Q285" s="2">
-        <v>14</v>
+      <c r="Q285" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="286" spans="1:17" x14ac:dyDescent="0.25">
@@ -15504,8 +15547,8 @@
       <c r="P286" s="2">
         <v>10.25</v>
       </c>
-      <c r="Q286" s="2">
-        <v>14</v>
+      <c r="Q286" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="287" spans="1:17" x14ac:dyDescent="0.25">
@@ -15557,8 +15600,8 @@
       <c r="P287" s="2">
         <v>10.23</v>
       </c>
-      <c r="Q287" s="2">
-        <v>14</v>
+      <c r="Q287" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="288" spans="1:17" x14ac:dyDescent="0.25">
@@ -15610,8 +15653,8 @@
       <c r="P288" s="2">
         <v>10.220000000000001</v>
       </c>
-      <c r="Q288" s="2">
-        <v>14</v>
+      <c r="Q288" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="289" spans="1:17" x14ac:dyDescent="0.25">
@@ -15663,8 +15706,8 @@
       <c r="P289" s="2">
         <v>10.210000000000001</v>
       </c>
-      <c r="Q289" s="2">
-        <v>14</v>
+      <c r="Q289" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="290" spans="1:17" x14ac:dyDescent="0.25">
@@ -15716,8 +15759,8 @@
       <c r="P290" s="2">
         <v>10.19</v>
       </c>
-      <c r="Q290" s="2">
-        <v>14</v>
+      <c r="Q290" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="291" spans="1:17" x14ac:dyDescent="0.25">
@@ -15769,8 +15812,8 @@
       <c r="P291" s="2">
         <v>10.51</v>
       </c>
-      <c r="Q291" s="2">
-        <v>14</v>
+      <c r="Q291" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="292" spans="1:17" x14ac:dyDescent="0.25">
@@ -15822,8 +15865,8 @@
       <c r="P292" s="2">
         <v>10.5</v>
       </c>
-      <c r="Q292" s="2">
-        <v>14</v>
+      <c r="Q292" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="293" spans="1:17" x14ac:dyDescent="0.25">
@@ -15875,8 +15918,8 @@
       <c r="P293" s="2">
         <v>10.48</v>
       </c>
-      <c r="Q293" s="2">
-        <v>14</v>
+      <c r="Q293" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="294" spans="1:17" x14ac:dyDescent="0.25">
@@ -15928,8 +15971,8 @@
       <c r="P294" s="2">
         <v>10.47</v>
       </c>
-      <c r="Q294" s="2">
-        <v>14</v>
+      <c r="Q294" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="295" spans="1:17" x14ac:dyDescent="0.25">
@@ -15981,8 +16024,8 @@
       <c r="P295" s="2">
         <v>10.45</v>
       </c>
-      <c r="Q295" s="2">
-        <v>15</v>
+      <c r="Q295" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="296" spans="1:17" x14ac:dyDescent="0.25">
@@ -16034,8 +16077,8 @@
       <c r="P296" s="2">
         <v>10.77</v>
       </c>
-      <c r="Q296" s="2">
-        <v>15</v>
+      <c r="Q296" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="297" spans="1:17" x14ac:dyDescent="0.25">
@@ -16087,8 +16130,8 @@
       <c r="P297" s="2">
         <v>10.76</v>
       </c>
-      <c r="Q297" s="2">
-        <v>15</v>
+      <c r="Q297" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="298" spans="1:17" x14ac:dyDescent="0.25">
@@ -16140,8 +16183,8 @@
       <c r="P298" s="2">
         <v>10.75</v>
       </c>
-      <c r="Q298" s="2">
-        <v>15</v>
+      <c r="Q298" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="299" spans="1:17" x14ac:dyDescent="0.25">
@@ -16193,8 +16236,8 @@
       <c r="P299" s="2">
         <v>11.07</v>
       </c>
-      <c r="Q299" s="2">
-        <v>15</v>
+      <c r="Q299" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="300" spans="1:17" x14ac:dyDescent="0.25">
@@ -16246,8 +16289,8 @@
       <c r="P300" s="2">
         <v>11.05</v>
       </c>
-      <c r="Q300" s="2">
-        <v>15</v>
+      <c r="Q300" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="301" spans="1:17" x14ac:dyDescent="0.25">
@@ -16299,8 +16342,8 @@
       <c r="P301" s="2">
         <v>11.04</v>
       </c>
-      <c r="Q301" s="2">
-        <v>15</v>
+      <c r="Q301" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="302" spans="1:17" x14ac:dyDescent="0.25">
@@ -16352,8 +16395,8 @@
       <c r="P302" s="2">
         <v>11.03</v>
       </c>
-      <c r="Q302" s="2">
-        <v>15</v>
+      <c r="Q302" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="303" spans="1:17" x14ac:dyDescent="0.25">
@@ -16405,8 +16448,8 @@
       <c r="P303" s="2">
         <v>11.01</v>
       </c>
-      <c r="Q303" s="2">
-        <v>15</v>
+      <c r="Q303" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="304" spans="1:17" x14ac:dyDescent="0.25">
@@ -16458,8 +16501,8 @@
       <c r="P304" s="2">
         <v>11</v>
       </c>
-      <c r="Q304" s="2">
-        <v>15</v>
+      <c r="Q304" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="305" spans="1:17" x14ac:dyDescent="0.25">
@@ -16511,8 +16554,8 @@
       <c r="P305" s="2">
         <v>10.98</v>
       </c>
-      <c r="Q305" s="2">
-        <v>15</v>
+      <c r="Q305" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="306" spans="1:17" x14ac:dyDescent="0.25">
@@ -16564,8 +16607,8 @@
       <c r="P306" s="2">
         <v>11.31</v>
       </c>
-      <c r="Q306" s="2">
-        <v>15</v>
+      <c r="Q306" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="307" spans="1:17" x14ac:dyDescent="0.25">
@@ -16617,8 +16660,8 @@
       <c r="P307" s="2">
         <v>11.3</v>
       </c>
-      <c r="Q307" s="2">
-        <v>15</v>
+      <c r="Q307" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="308" spans="1:17" x14ac:dyDescent="0.25">
@@ -16670,8 +16713,8 @@
       <c r="P308" s="2">
         <v>11.28</v>
       </c>
-      <c r="Q308" s="2">
-        <v>15</v>
+      <c r="Q308" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="309" spans="1:17" x14ac:dyDescent="0.25">
@@ -16723,8 +16766,8 @@
       <c r="P309" s="2">
         <v>11.27</v>
       </c>
-      <c r="Q309" s="2">
-        <v>15</v>
+      <c r="Q309" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="310" spans="1:17" x14ac:dyDescent="0.25">
@@ -16776,8 +16819,8 @@
       <c r="P310" s="2">
         <v>11.26</v>
       </c>
-      <c r="Q310" s="2">
-        <v>15</v>
+      <c r="Q310" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="311" spans="1:17" x14ac:dyDescent="0.25">
@@ -16829,8 +16872,8 @@
       <c r="P311" s="2">
         <v>11.24</v>
       </c>
-      <c r="Q311" s="2">
-        <v>15</v>
+      <c r="Q311" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="312" spans="1:17" x14ac:dyDescent="0.25">
@@ -16882,8 +16925,8 @@
       <c r="P312" s="2">
         <v>11.23</v>
       </c>
-      <c r="Q312" s="2">
-        <v>15</v>
+      <c r="Q312" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="313" spans="1:17" x14ac:dyDescent="0.25">
@@ -16935,8 +16978,8 @@
       <c r="P313" s="2">
         <v>11.55</v>
       </c>
-      <c r="Q313" s="2">
-        <v>15</v>
+      <c r="Q313" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="314" spans="1:17" x14ac:dyDescent="0.25">
@@ -16988,8 +17031,8 @@
       <c r="P314" s="2">
         <v>11.54</v>
       </c>
-      <c r="Q314" s="2">
-        <v>15</v>
+      <c r="Q314" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="315" spans="1:17" x14ac:dyDescent="0.25">
@@ -17041,8 +17084,8 @@
       <c r="P315" s="2">
         <v>11.53</v>
       </c>
-      <c r="Q315" s="2">
-        <v>15</v>
+      <c r="Q315" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="316" spans="1:17" x14ac:dyDescent="0.25">
@@ -17094,8 +17137,8 @@
       <c r="P316" s="2">
         <v>11.52</v>
       </c>
-      <c r="Q316" s="2">
-        <v>15</v>
+      <c r="Q316" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="317" spans="1:17" x14ac:dyDescent="0.25">
@@ -17147,8 +17190,8 @@
       <c r="P317" s="2">
         <v>11.5</v>
       </c>
-      <c r="Q317" s="2">
-        <v>15</v>
+      <c r="Q317" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="318" spans="1:17" x14ac:dyDescent="0.25">
@@ -17200,8 +17243,8 @@
       <c r="P318" s="2">
         <v>11.56</v>
       </c>
-      <c r="Q318" s="2">
-        <v>15</v>
+      <c r="Q318" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="319" spans="1:17" x14ac:dyDescent="0.25">
@@ -17253,8 +17296,8 @@
       <c r="P319" s="2">
         <v>11.49</v>
       </c>
-      <c r="Q319" s="2">
-        <v>15</v>
+      <c r="Q319" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="320" spans="1:17" x14ac:dyDescent="0.25">
@@ -17306,8 +17349,8 @@
       <c r="P320" s="2">
         <v>11.83</v>
       </c>
-      <c r="Q320" s="2">
-        <v>15</v>
+      <c r="Q320" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="321" spans="1:17" x14ac:dyDescent="0.25">
@@ -76667,7 +76710,7 @@
         <v>11.88</v>
       </c>
       <c r="Q1440" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1441" spans="1:17" x14ac:dyDescent="0.25">
@@ -76719,8 +76762,8 @@
       <c r="P1441" s="1">
         <v>1.6819999999999999</v>
       </c>
-      <c r="Q1441" s="2">
-        <v>9</v>
+      <c r="Q1441" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1442" spans="1:17" x14ac:dyDescent="0.25">
@@ -76772,8 +76815,8 @@
       <c r="P1442" s="1">
         <v>1.6220000000000001</v>
       </c>
-      <c r="Q1442" s="2">
-        <v>9</v>
+      <c r="Q1442" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1443" spans="1:17" x14ac:dyDescent="0.25">
@@ -76825,8 +76868,8 @@
       <c r="P1443" s="1">
         <v>1.605</v>
       </c>
-      <c r="Q1443" s="2">
-        <v>9</v>
+      <c r="Q1443" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1444" spans="1:17" x14ac:dyDescent="0.25">
@@ -76878,8 +76921,8 @@
       <c r="P1444" s="1">
         <v>1.7110000000000001</v>
       </c>
-      <c r="Q1444" s="2">
-        <v>9</v>
+      <c r="Q1444" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1445" spans="1:17" x14ac:dyDescent="0.25">
@@ -76931,8 +76974,8 @@
       <c r="P1445" s="1">
         <v>1.69</v>
       </c>
-      <c r="Q1445" s="2">
-        <v>9</v>
+      <c r="Q1445" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1446" spans="1:17" x14ac:dyDescent="0.25">
@@ -76984,8 +77027,8 @@
       <c r="P1446" s="1">
         <v>1.6419999999999999</v>
       </c>
-      <c r="Q1446" s="2">
-        <v>9</v>
+      <c r="Q1446" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1447" spans="1:17" x14ac:dyDescent="0.25">
@@ -77037,8 +77080,8 @@
       <c r="P1447" s="1">
         <v>1.952</v>
       </c>
-      <c r="Q1447" s="2">
-        <v>9</v>
+      <c r="Q1447" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1448" spans="1:17" x14ac:dyDescent="0.25">
@@ -77090,8 +77133,8 @@
       <c r="P1448" s="1">
         <v>1.917</v>
       </c>
-      <c r="Q1448" s="2">
-        <v>9</v>
+      <c r="Q1448" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1449" spans="1:17" x14ac:dyDescent="0.25">
@@ -77143,8 +77186,8 @@
       <c r="P1449" s="1">
         <v>1.891</v>
       </c>
-      <c r="Q1449" s="2">
-        <v>9</v>
+      <c r="Q1449" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1450" spans="1:17" x14ac:dyDescent="0.25">
@@ -77196,8 +77239,8 @@
       <c r="P1450" s="1">
         <v>2.218</v>
       </c>
-      <c r="Q1450" s="2">
-        <v>9</v>
+      <c r="Q1450" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1451" spans="1:17" x14ac:dyDescent="0.25">
@@ -77249,8 +77292,8 @@
       <c r="P1451" s="1">
         <v>2.1800000000000002</v>
       </c>
-      <c r="Q1451" s="2">
-        <v>9</v>
+      <c r="Q1451" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1452" spans="1:17" x14ac:dyDescent="0.25">
@@ -77302,8 +77345,8 @@
       <c r="P1452" s="1">
         <v>2.1509999999999998</v>
       </c>
-      <c r="Q1452" s="2">
-        <v>9</v>
+      <c r="Q1452" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1453" spans="1:17" x14ac:dyDescent="0.25">
@@ -77355,8 +77398,8 @@
       <c r="P1453" s="1">
         <v>2.5099999999999998</v>
       </c>
-      <c r="Q1453" s="2">
-        <v>9</v>
+      <c r="Q1453" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1454" spans="1:17" x14ac:dyDescent="0.25">
@@ -77408,8 +77451,8 @@
       <c r="P1454" s="1">
         <v>2.4769999999999999</v>
       </c>
-      <c r="Q1454" s="2">
-        <v>9</v>
+      <c r="Q1454" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1455" spans="1:17" x14ac:dyDescent="0.25">
@@ -77461,8 +77504,8 @@
       <c r="P1455" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="Q1455" s="2">
-        <v>9</v>
+      <c r="Q1455" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1456" spans="1:17" x14ac:dyDescent="0.25">
@@ -77514,8 +77557,8 @@
       <c r="P1456" s="1">
         <v>2.8290000000000002</v>
       </c>
-      <c r="Q1456" s="2">
-        <v>9</v>
+      <c r="Q1456" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1457" spans="1:17" x14ac:dyDescent="0.25">
@@ -77567,8 +77610,8 @@
       <c r="P1457" s="1">
         <v>2.7970000000000002</v>
       </c>
-      <c r="Q1457" s="2">
-        <v>9</v>
+      <c r="Q1457" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1458" spans="1:17" x14ac:dyDescent="0.25">
@@ -77620,8 +77663,8 @@
       <c r="P1458" s="1">
         <v>2.7709999999999999</v>
       </c>
-      <c r="Q1458" s="2">
-        <v>9</v>
+      <c r="Q1458" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1459" spans="1:17" x14ac:dyDescent="0.25">
@@ -77673,8 +77716,8 @@
       <c r="P1459" s="1">
         <v>3.173</v>
       </c>
-      <c r="Q1459" s="2">
-        <v>9</v>
+      <c r="Q1459" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1460" spans="1:17" x14ac:dyDescent="0.25">
@@ -77726,8 +77769,8 @@
       <c r="P1460" s="1">
         <v>3.1480000000000001</v>
       </c>
-      <c r="Q1460" s="2">
-        <v>9</v>
+      <c r="Q1460" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="1461" spans="1:17" x14ac:dyDescent="0.25">
@@ -77779,8 +77822,8 @@
       <c r="P1461" s="2">
         <v>3.1150000000000002</v>
       </c>
-      <c r="Q1461" s="2">
-        <v>13</v>
+      <c r="Q1461" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1462" spans="1:17" x14ac:dyDescent="0.25">
@@ -77832,8 +77875,8 @@
       <c r="P1462" s="2">
         <v>3.544</v>
       </c>
-      <c r="Q1462" s="2">
-        <v>13</v>
+      <c r="Q1462" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1463" spans="1:17" x14ac:dyDescent="0.25">
@@ -77885,8 +77928,8 @@
       <c r="P1463" s="2">
         <v>3.5059999999999998</v>
       </c>
-      <c r="Q1463" s="2">
-        <v>13</v>
+      <c r="Q1463" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1464" spans="1:17" x14ac:dyDescent="0.25">
@@ -77938,8 +77981,8 @@
       <c r="P1464" s="2">
         <v>3.7240000000000002</v>
       </c>
-      <c r="Q1464" s="2">
-        <v>13</v>
+      <c r="Q1464" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1465" spans="1:17" x14ac:dyDescent="0.25">
@@ -77991,8 +78034,8 @@
       <c r="P1465" s="2">
         <v>3.6960000000000002</v>
       </c>
-      <c r="Q1465" s="2">
-        <v>13</v>
+      <c r="Q1465" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1466" spans="1:17" x14ac:dyDescent="0.25">
@@ -78044,8 +78087,8 @@
       <c r="P1466" s="2">
         <v>3.681</v>
       </c>
-      <c r="Q1466" s="2">
-        <v>13</v>
+      <c r="Q1466" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1467" spans="1:17" x14ac:dyDescent="0.25">
@@ -78097,8 +78140,8 @@
       <c r="P1467" s="2">
         <v>3.89</v>
       </c>
-      <c r="Q1467" s="2">
-        <v>13</v>
+      <c r="Q1467" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1468" spans="1:17" x14ac:dyDescent="0.25">
@@ -78150,8 +78193,8 @@
       <c r="P1468" s="2">
         <v>3.8639999999999999</v>
       </c>
-      <c r="Q1468" s="2">
-        <v>13</v>
+      <c r="Q1468" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1469" spans="1:17" x14ac:dyDescent="0.25">
@@ -78203,8 +78246,8 @@
       <c r="P1469" s="2">
         <v>3.83</v>
       </c>
-      <c r="Q1469" s="2">
-        <v>13</v>
+      <c r="Q1469" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1470" spans="1:17" x14ac:dyDescent="0.25">
@@ -78256,8 +78299,8 @@
       <c r="P1470" s="2">
         <v>4.05</v>
       </c>
-      <c r="Q1470" s="2">
-        <v>13</v>
+      <c r="Q1470" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1471" spans="1:17" x14ac:dyDescent="0.25">
@@ -78309,8 +78352,8 @@
       <c r="P1471" s="2">
         <v>4.0250000000000004</v>
       </c>
-      <c r="Q1471" s="2">
-        <v>13</v>
+      <c r="Q1471" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1472" spans="1:17" x14ac:dyDescent="0.25">
@@ -78362,8 +78405,8 @@
       <c r="P1472" s="2">
         <v>3.9980000000000002</v>
       </c>
-      <c r="Q1472" s="2">
-        <v>13</v>
+      <c r="Q1472" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1473" spans="1:17" x14ac:dyDescent="0.25">
@@ -78415,8 +78458,8 @@
       <c r="P1473" s="2">
         <v>4.2229999999999999</v>
       </c>
-      <c r="Q1473" s="2">
-        <v>13</v>
+      <c r="Q1473" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1474" spans="1:17" x14ac:dyDescent="0.25">
@@ -78468,8 +78511,8 @@
       <c r="P1474" s="2">
         <v>4.1989999999999998</v>
       </c>
-      <c r="Q1474" s="2">
-        <v>13</v>
+      <c r="Q1474" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1475" spans="1:17" x14ac:dyDescent="0.25">
@@ -78521,8 +78564,8 @@
       <c r="P1475" s="2">
         <v>4.1740000000000004</v>
       </c>
-      <c r="Q1475" s="2">
-        <v>13</v>
+      <c r="Q1475" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1476" spans="1:17" x14ac:dyDescent="0.25">
@@ -78574,8 +78617,8 @@
       <c r="P1476" s="2">
         <v>4.41</v>
       </c>
-      <c r="Q1476" s="2">
-        <v>13</v>
+      <c r="Q1476" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1477" spans="1:17" x14ac:dyDescent="0.25">
@@ -78627,8 +78670,8 @@
       <c r="P1477" s="2">
         <v>4.38</v>
       </c>
-      <c r="Q1477" s="2">
-        <v>13</v>
+      <c r="Q1477" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1478" spans="1:17" x14ac:dyDescent="0.25">
@@ -78680,8 +78723,8 @@
       <c r="P1478" s="2">
         <v>4.3559999999999999</v>
       </c>
-      <c r="Q1478" s="2">
-        <v>13</v>
+      <c r="Q1478" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1479" spans="1:17" x14ac:dyDescent="0.25">
@@ -78733,8 +78776,8 @@
       <c r="P1479" s="2">
         <v>4.7210000000000001</v>
       </c>
-      <c r="Q1479" s="2">
-        <v>13</v>
+      <c r="Q1479" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1480" spans="1:17" x14ac:dyDescent="0.25">
@@ -78786,8 +78829,8 @@
       <c r="P1480" s="2">
         <v>4.7009999999999996</v>
       </c>
-      <c r="Q1480" s="2">
-        <v>13</v>
+      <c r="Q1480" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="1481" spans="1:17" x14ac:dyDescent="0.25">
@@ -78839,8 +78882,8 @@
       <c r="P1481" s="2">
         <v>4.54</v>
       </c>
-      <c r="Q1481" s="2">
-        <v>16</v>
+      <c r="Q1481" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1482" spans="1:17" x14ac:dyDescent="0.25">
@@ -78892,8 +78935,8 @@
       <c r="P1482" s="2">
         <v>4.78</v>
       </c>
-      <c r="Q1482" s="2">
-        <v>16</v>
+      <c r="Q1482" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1483" spans="1:17" x14ac:dyDescent="0.25">
@@ -78945,8 +78988,8 @@
       <c r="P1483" s="2">
         <v>4.76</v>
       </c>
-      <c r="Q1483" s="2">
-        <v>16</v>
+      <c r="Q1483" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1484" spans="1:17" x14ac:dyDescent="0.25">
@@ -78998,8 +79041,8 @@
       <c r="P1484" s="2">
         <v>4.74</v>
       </c>
-      <c r="Q1484" s="2">
-        <v>16</v>
+      <c r="Q1484" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1485" spans="1:17" x14ac:dyDescent="0.25">
@@ -79051,8 +79094,8 @@
       <c r="P1485" s="2">
         <v>4.9850000000000003</v>
       </c>
-      <c r="Q1485" s="2">
-        <v>16</v>
+      <c r="Q1485" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1486" spans="1:17" x14ac:dyDescent="0.25">
@@ -79104,8 +79147,8 @@
       <c r="P1486" s="2">
         <v>4.9630000000000001</v>
       </c>
-      <c r="Q1486" s="2">
-        <v>16</v>
+      <c r="Q1486" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1487" spans="1:17" x14ac:dyDescent="0.25">
@@ -79157,8 +79200,8 @@
       <c r="P1487" s="2">
         <v>4.9400000000000004</v>
       </c>
-      <c r="Q1487" s="2">
-        <v>16</v>
+      <c r="Q1487" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1488" spans="1:17" x14ac:dyDescent="0.25">
@@ -79210,8 +79253,8 @@
       <c r="P1488" s="2">
         <v>5.19</v>
       </c>
-      <c r="Q1488" s="2">
-        <v>16</v>
+      <c r="Q1488" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1489" spans="1:17" x14ac:dyDescent="0.25">
@@ -79263,8 +79306,8 @@
       <c r="P1489" s="2">
         <v>5.1680000000000001</v>
       </c>
-      <c r="Q1489" s="2">
-        <v>16</v>
+      <c r="Q1489" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1490" spans="1:17" x14ac:dyDescent="0.25">
@@ -79316,8 +79359,8 @@
       <c r="P1490" s="2">
         <v>5.1449999999999996</v>
       </c>
-      <c r="Q1490" s="2">
-        <v>16</v>
+      <c r="Q1490" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1491" spans="1:17" x14ac:dyDescent="0.25">
@@ -79369,8 +79412,8 @@
       <c r="P1491" s="2">
         <v>5.399</v>
       </c>
-      <c r="Q1491" s="2">
-        <v>16</v>
+      <c r="Q1491" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1492" spans="1:17" x14ac:dyDescent="0.25">
@@ -79422,8 +79465,8 @@
       <c r="P1492" s="2">
         <v>5.375</v>
       </c>
-      <c r="Q1492" s="2">
-        <v>16</v>
+      <c r="Q1492" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1493" spans="1:17" x14ac:dyDescent="0.25">
@@ -79475,8 +79518,8 @@
       <c r="P1493" s="2">
         <v>5.35</v>
       </c>
-      <c r="Q1493" s="2">
-        <v>16</v>
+      <c r="Q1493" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1494" spans="1:17" x14ac:dyDescent="0.25">
@@ -79528,8 +79571,8 @@
       <c r="P1494" s="2">
         <v>5.609</v>
       </c>
-      <c r="Q1494" s="2">
-        <v>16</v>
+      <c r="Q1494" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1495" spans="1:17" x14ac:dyDescent="0.25">
@@ -79581,8 +79624,8 @@
       <c r="P1495" s="2">
         <v>5.593</v>
       </c>
-      <c r="Q1495" s="2">
-        <v>16</v>
+      <c r="Q1495" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1496" spans="1:17" x14ac:dyDescent="0.25">
@@ -79634,8 +79677,8 @@
       <c r="P1496" s="2">
         <v>5.5739999999999998</v>
       </c>
-      <c r="Q1496" s="2">
-        <v>16</v>
+      <c r="Q1496" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1497" spans="1:17" x14ac:dyDescent="0.25">
@@ -79687,8 +79730,8 @@
       <c r="P1497" s="2">
         <v>5.9809999999999999</v>
       </c>
-      <c r="Q1497" s="2">
-        <v>16</v>
+      <c r="Q1497" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1498" spans="1:17" x14ac:dyDescent="0.25">
@@ -79740,8 +79783,8 @@
       <c r="P1498" s="2">
         <v>5.8170000000000002</v>
       </c>
-      <c r="Q1498" s="2">
-        <v>16</v>
+      <c r="Q1498" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1499" spans="1:17" x14ac:dyDescent="0.25">
@@ -79793,8 +79836,8 @@
       <c r="P1499" s="2">
         <v>5.81</v>
       </c>
-      <c r="Q1499" s="2">
-        <v>16</v>
+      <c r="Q1499" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1500" spans="1:17" x14ac:dyDescent="0.25">
@@ -79846,8 +79889,8 @@
       <c r="P1500" s="2">
         <v>6.06</v>
       </c>
-      <c r="Q1500" s="2">
-        <v>16</v>
+      <c r="Q1500" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="1501" spans="1:17" x14ac:dyDescent="0.25">
@@ -79899,8 +79942,8 @@
       <c r="P1501" s="2">
         <v>6.0439999999999996</v>
       </c>
-      <c r="Q1501" s="2">
-        <v>17</v>
+      <c r="Q1501" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1502" spans="1:17" x14ac:dyDescent="0.25">
@@ -79952,8 +79995,8 @@
       <c r="P1502" s="2">
         <v>6.024</v>
       </c>
-      <c r="Q1502" s="2">
-        <v>17</v>
+      <c r="Q1502" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1503" spans="1:17" x14ac:dyDescent="0.25">
@@ -80005,8 +80048,8 @@
       <c r="P1503" s="2">
         <v>6</v>
       </c>
-      <c r="Q1503" s="2">
-        <v>17</v>
+      <c r="Q1503" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1504" spans="1:17" x14ac:dyDescent="0.25">
@@ -80058,8 +80101,8 @@
       <c r="P1504" s="2">
         <v>6.274</v>
       </c>
-      <c r="Q1504" s="2">
-        <v>17</v>
+      <c r="Q1504" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1505" spans="1:17" x14ac:dyDescent="0.25">
@@ -80111,8 +80154,8 @@
       <c r="P1505" s="2">
         <v>6.2539999999999996</v>
       </c>
-      <c r="Q1505" s="2">
-        <v>17</v>
+      <c r="Q1505" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1506" spans="1:17" x14ac:dyDescent="0.25">
@@ -80164,8 +80207,8 @@
       <c r="P1506" s="2">
         <v>6.2329999999999997</v>
       </c>
-      <c r="Q1506" s="2">
-        <v>17</v>
+      <c r="Q1506" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1507" spans="1:17" x14ac:dyDescent="0.25">
@@ -80217,8 +80260,8 @@
       <c r="P1507" s="2">
         <v>6.2149999999999999</v>
       </c>
-      <c r="Q1507" s="2">
-        <v>17</v>
+      <c r="Q1507" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1508" spans="1:17" x14ac:dyDescent="0.25">
@@ -80270,8 +80313,8 @@
       <c r="P1508" s="2">
         <v>6.49</v>
       </c>
-      <c r="Q1508" s="2">
-        <v>17</v>
+      <c r="Q1508" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1509" spans="1:17" x14ac:dyDescent="0.25">
@@ -80323,8 +80366,8 @@
       <c r="P1509" s="2">
         <v>6.47</v>
       </c>
-      <c r="Q1509" s="2">
-        <v>17</v>
+      <c r="Q1509" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1510" spans="1:17" x14ac:dyDescent="0.25">
@@ -80376,8 +80419,8 @@
       <c r="P1510" s="2">
         <v>6.4509999999999996</v>
       </c>
-      <c r="Q1510" s="2">
-        <v>17</v>
+      <c r="Q1510" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1511" spans="1:17" x14ac:dyDescent="0.25">
@@ -80429,8 +80472,8 @@
       <c r="P1511" s="2">
         <v>6.4329999999999998</v>
       </c>
-      <c r="Q1511" s="2">
-        <v>17</v>
+      <c r="Q1511" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1512" spans="1:17" x14ac:dyDescent="0.25">
@@ -80482,8 +80525,8 @@
       <c r="P1512" s="2">
         <v>6.71</v>
       </c>
-      <c r="Q1512" s="2">
-        <v>17</v>
+      <c r="Q1512" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1513" spans="1:17" x14ac:dyDescent="0.25">
@@ -80535,8 +80578,8 @@
       <c r="P1513" s="2">
         <v>6.6920000000000002</v>
       </c>
-      <c r="Q1513" s="2">
-        <v>17</v>
+      <c r="Q1513" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1514" spans="1:17" x14ac:dyDescent="0.25">
@@ -80588,8 +80631,8 @@
       <c r="P1514" s="2">
         <v>6.67</v>
       </c>
-      <c r="Q1514" s="2">
-        <v>17</v>
+      <c r="Q1514" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1515" spans="1:17" x14ac:dyDescent="0.25">
@@ -80641,8 +80684,8 @@
       <c r="P1515" s="2">
         <v>6.9530000000000003</v>
       </c>
-      <c r="Q1515" s="2">
-        <v>17</v>
+      <c r="Q1515" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1516" spans="1:17" x14ac:dyDescent="0.25">
@@ -80694,8 +80737,8 @@
       <c r="P1516" s="2">
         <v>6.9359999999999999</v>
       </c>
-      <c r="Q1516" s="2">
-        <v>17</v>
+      <c r="Q1516" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1517" spans="1:17" x14ac:dyDescent="0.25">
@@ -80747,8 +80790,8 @@
       <c r="P1517" s="2">
         <v>6.9180000000000001</v>
       </c>
-      <c r="Q1517" s="2">
-        <v>17</v>
+      <c r="Q1517" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1518" spans="1:17" x14ac:dyDescent="0.25">
@@ -80800,8 +80843,8 @@
       <c r="P1518" s="2">
         <v>7.202</v>
       </c>
-      <c r="Q1518" s="2">
-        <v>17</v>
+      <c r="Q1518" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1519" spans="1:17" x14ac:dyDescent="0.25">
@@ -80853,8 +80896,8 @@
       <c r="P1519" s="2">
         <v>7.1840000000000002</v>
       </c>
-      <c r="Q1519" s="2">
-        <v>17</v>
+      <c r="Q1519" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1520" spans="1:17" x14ac:dyDescent="0.25">
@@ -80906,8 +80949,8 @@
       <c r="P1520" s="2">
         <v>7.1660000000000004</v>
       </c>
-      <c r="Q1520" s="2">
-        <v>17</v>
+      <c r="Q1520" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="1521" spans="1:17" x14ac:dyDescent="0.25">
@@ -80959,8 +81002,8 @@
       <c r="P1521" s="2">
         <v>7.45</v>
       </c>
-      <c r="Q1521" s="2">
-        <v>18</v>
+      <c r="Q1521" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1522" spans="1:17" x14ac:dyDescent="0.25">
@@ -81012,8 +81055,8 @@
       <c r="P1522" s="2">
         <v>7.4379999999999997</v>
       </c>
-      <c r="Q1522" s="2">
-        <v>18</v>
+      <c r="Q1522" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1523" spans="1:17" x14ac:dyDescent="0.25">
@@ -81065,8 +81108,8 @@
       <c r="P1523" s="2">
         <v>7.4180000000000001</v>
       </c>
-      <c r="Q1523" s="2">
-        <v>18</v>
+      <c r="Q1523" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1524" spans="1:17" x14ac:dyDescent="0.25">
@@ -81118,8 +81161,8 @@
       <c r="P1524" s="2">
         <v>7.7069999999999999</v>
       </c>
-      <c r="Q1524" s="2">
-        <v>18</v>
+      <c r="Q1524" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1525" spans="1:17" x14ac:dyDescent="0.25">
@@ -81171,8 +81214,8 @@
       <c r="P1525" s="2">
         <v>7.69</v>
       </c>
-      <c r="Q1525" s="2">
-        <v>18</v>
+      <c r="Q1525" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1526" spans="1:17" x14ac:dyDescent="0.25">
@@ -81224,8 +81267,8 @@
       <c r="P1526" s="2">
         <v>7.6760000000000002</v>
       </c>
-      <c r="Q1526" s="2">
-        <v>18</v>
+      <c r="Q1526" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1527" spans="1:17" x14ac:dyDescent="0.25">
@@ -81277,8 +81320,8 @@
       <c r="P1527" s="2">
         <v>7.6559999999999997</v>
       </c>
-      <c r="Q1527" s="2">
-        <v>18</v>
+      <c r="Q1527" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1528" spans="1:17" x14ac:dyDescent="0.25">
@@ -81330,8 +81373,8 @@
       <c r="P1528" s="2">
         <v>7.9489999999999998</v>
       </c>
-      <c r="Q1528" s="2">
-        <v>18</v>
+      <c r="Q1528" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1529" spans="1:17" x14ac:dyDescent="0.25">
@@ -81383,8 +81426,8 @@
       <c r="P1529" s="2">
         <v>7.9320000000000004</v>
       </c>
-      <c r="Q1529" s="2">
-        <v>18</v>
+      <c r="Q1529" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1530" spans="1:17" x14ac:dyDescent="0.25">
@@ -81436,8 +81479,8 @@
       <c r="P1530" s="2">
         <v>7.9139999999999997</v>
       </c>
-      <c r="Q1530" s="2">
-        <v>18</v>
+      <c r="Q1530" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1531" spans="1:17" x14ac:dyDescent="0.25">
@@ -81489,8 +81532,8 @@
       <c r="P1531" s="2">
         <v>7.891</v>
       </c>
-      <c r="Q1531" s="2">
-        <v>18</v>
+      <c r="Q1531" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1532" spans="1:17" x14ac:dyDescent="0.25">
@@ -81542,8 +81585,8 @@
       <c r="P1532" s="2">
         <v>8.1920000000000002</v>
       </c>
-      <c r="Q1532" s="2">
-        <v>18</v>
+      <c r="Q1532" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1533" spans="1:17" x14ac:dyDescent="0.25">
@@ -81595,8 +81638,8 @@
       <c r="P1533" s="2">
         <v>8.1780000000000008</v>
       </c>
-      <c r="Q1533" s="2">
-        <v>18</v>
+      <c r="Q1533" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1534" spans="1:17" x14ac:dyDescent="0.25">
@@ -81648,8 +81691,8 @@
       <c r="P1534" s="2">
         <v>8.1630000000000003</v>
       </c>
-      <c r="Q1534" s="2">
-        <v>18</v>
+      <c r="Q1534" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1535" spans="1:17" x14ac:dyDescent="0.25">
@@ -81701,8 +81744,8 @@
       <c r="P1535" s="2">
         <v>8.1449999999999996</v>
       </c>
-      <c r="Q1535" s="2">
-        <v>18</v>
+      <c r="Q1535" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1536" spans="1:17" x14ac:dyDescent="0.25">
@@ -81754,8 +81797,8 @@
       <c r="P1536" s="2">
         <v>8.44</v>
       </c>
-      <c r="Q1536" s="2">
-        <v>18</v>
+      <c r="Q1536" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1537" spans="1:17" x14ac:dyDescent="0.25">
@@ -81807,8 +81850,8 @@
       <c r="P1537" s="2">
         <v>8.4269999999999996</v>
       </c>
-      <c r="Q1537" s="2">
-        <v>18</v>
+      <c r="Q1537" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1538" spans="1:17" x14ac:dyDescent="0.25">
@@ -81860,8 +81903,8 @@
       <c r="P1538" s="2">
         <v>8.4079999999999995</v>
       </c>
-      <c r="Q1538" s="2">
-        <v>18</v>
+      <c r="Q1538" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1539" spans="1:17" x14ac:dyDescent="0.25">
@@ -81913,8 +81956,8 @@
       <c r="P1539" s="2">
         <v>8.3949999999999996</v>
       </c>
-      <c r="Q1539" s="2">
-        <v>18</v>
+      <c r="Q1539" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1540" spans="1:17" x14ac:dyDescent="0.25">
@@ -81966,8 +82009,8 @@
       <c r="P1540" s="2">
         <v>8.3789999999999996</v>
       </c>
-      <c r="Q1540" s="2">
-        <v>18</v>
+      <c r="Q1540" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="1541" spans="1:17" x14ac:dyDescent="0.25">
@@ -82019,8 +82062,8 @@
       <c r="P1541" s="2">
         <v>0</v>
       </c>
-      <c r="Q1541" s="2">
-        <v>19</v>
+      <c r="Q1541" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1542" spans="1:17" x14ac:dyDescent="0.25">
@@ -82072,8 +82115,8 @@
       <c r="P1542" s="2">
         <v>0</v>
       </c>
-      <c r="Q1542" s="2">
-        <v>19</v>
+      <c r="Q1542" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1543" spans="1:17" x14ac:dyDescent="0.25">
@@ -82125,8 +82168,8 @@
       <c r="P1543" s="2">
         <v>0</v>
       </c>
-      <c r="Q1543" s="2">
-        <v>19</v>
+      <c r="Q1543" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1544" spans="1:17" x14ac:dyDescent="0.25">
@@ -82178,8 +82221,8 @@
       <c r="P1544" s="2">
         <v>0</v>
       </c>
-      <c r="Q1544" s="2">
-        <v>19</v>
+      <c r="Q1544" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1545" spans="1:17" x14ac:dyDescent="0.25">
@@ -82231,8 +82274,8 @@
       <c r="P1545" s="2">
         <v>0</v>
       </c>
-      <c r="Q1545" s="2">
-        <v>19</v>
+      <c r="Q1545" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1546" spans="1:17" x14ac:dyDescent="0.25">
@@ -82284,8 +82327,8 @@
       <c r="P1546" s="2">
         <v>0</v>
       </c>
-      <c r="Q1546" s="2">
-        <v>19</v>
+      <c r="Q1546" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1547" spans="1:17" x14ac:dyDescent="0.25">
@@ -82337,8 +82380,8 @@
       <c r="P1547" s="2">
         <v>0</v>
       </c>
-      <c r="Q1547" s="2">
-        <v>19</v>
+      <c r="Q1547" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1548" spans="1:17" x14ac:dyDescent="0.25">
@@ -82390,8 +82433,8 @@
       <c r="P1548" s="2">
         <v>0</v>
       </c>
-      <c r="Q1548" s="2">
-        <v>19</v>
+      <c r="Q1548" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1549" spans="1:17" x14ac:dyDescent="0.25">
@@ -82443,8 +82486,8 @@
       <c r="P1549" s="2">
         <v>0</v>
       </c>
-      <c r="Q1549" s="2">
-        <v>19</v>
+      <c r="Q1549" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1550" spans="1:17" x14ac:dyDescent="0.25">
@@ -82496,8 +82539,8 @@
       <c r="P1550" s="2">
         <v>0</v>
       </c>
-      <c r="Q1550" s="2">
-        <v>19</v>
+      <c r="Q1550" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1551" spans="1:17" x14ac:dyDescent="0.25">
@@ -82549,8 +82592,8 @@
       <c r="P1551" s="2">
         <v>0</v>
       </c>
-      <c r="Q1551" s="2">
-        <v>19</v>
+      <c r="Q1551" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1552" spans="1:17" x14ac:dyDescent="0.25">
@@ -82602,8 +82645,8 @@
       <c r="P1552" s="2">
         <v>0</v>
       </c>
-      <c r="Q1552" s="2">
-        <v>19</v>
+      <c r="Q1552" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1553" spans="1:17" x14ac:dyDescent="0.25">
@@ -82655,8 +82698,8 @@
       <c r="P1553" s="2">
         <v>0</v>
       </c>
-      <c r="Q1553" s="2">
-        <v>19</v>
+      <c r="Q1553" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1554" spans="1:17" x14ac:dyDescent="0.25">
@@ -82708,8 +82751,8 @@
       <c r="P1554" s="2">
         <v>0</v>
       </c>
-      <c r="Q1554" s="2">
-        <v>19</v>
+      <c r="Q1554" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1555" spans="1:17" x14ac:dyDescent="0.25">
@@ -82761,8 +82804,8 @@
       <c r="P1555" s="2">
         <v>0</v>
       </c>
-      <c r="Q1555" s="2">
-        <v>19</v>
+      <c r="Q1555" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1556" spans="1:17" x14ac:dyDescent="0.25">
@@ -82814,8 +82857,8 @@
       <c r="P1556" s="2">
         <v>0</v>
       </c>
-      <c r="Q1556" s="2">
-        <v>19</v>
+      <c r="Q1556" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1557" spans="1:17" x14ac:dyDescent="0.25">
@@ -82867,8 +82910,8 @@
       <c r="P1557" s="2">
         <v>0</v>
       </c>
-      <c r="Q1557" s="2">
-        <v>19</v>
+      <c r="Q1557" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1558" spans="1:17" x14ac:dyDescent="0.25">
@@ -82920,8 +82963,8 @@
       <c r="P1558" s="2">
         <v>0</v>
       </c>
-      <c r="Q1558" s="2">
-        <v>19</v>
+      <c r="Q1558" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1559" spans="1:17" x14ac:dyDescent="0.25">
@@ -82973,8 +83016,8 @@
       <c r="P1559" s="2">
         <v>0</v>
       </c>
-      <c r="Q1559" s="2">
-        <v>19</v>
+      <c r="Q1559" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1560" spans="1:17" x14ac:dyDescent="0.25">
@@ -83026,8 +83069,8 @@
       <c r="P1560" s="2">
         <v>0</v>
       </c>
-      <c r="Q1560" s="2">
-        <v>19</v>
+      <c r="Q1560" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="1561" spans="1:17" x14ac:dyDescent="0.25">
@@ -83079,8 +83122,8 @@
       <c r="P1561" s="2">
         <v>9.99</v>
       </c>
-      <c r="Q1561" s="2">
-        <v>20</v>
+      <c r="Q1561" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1562" spans="1:17" x14ac:dyDescent="0.25">
@@ -83132,8 +83175,8 @@
       <c r="P1562" s="2">
         <v>9.9760000000000009</v>
       </c>
-      <c r="Q1562" s="2">
-        <v>20</v>
+      <c r="Q1562" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1563" spans="1:17" x14ac:dyDescent="0.25">
@@ -83185,8 +83228,8 @@
       <c r="P1563" s="2">
         <v>9.9629999999999992</v>
       </c>
-      <c r="Q1563" s="2">
-        <v>20</v>
+      <c r="Q1563" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1564" spans="1:17" x14ac:dyDescent="0.25">
@@ -83238,8 +83281,8 @@
       <c r="P1564" s="2">
         <v>9.9489999999999998</v>
       </c>
-      <c r="Q1564" s="2">
-        <v>20</v>
+      <c r="Q1564" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1565" spans="1:17" x14ac:dyDescent="0.25">
@@ -83291,8 +83334,8 @@
       <c r="P1565" s="2">
         <v>9.9339999999999993</v>
       </c>
-      <c r="Q1565" s="2">
-        <v>20</v>
+      <c r="Q1565" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1566" spans="1:17" x14ac:dyDescent="0.25">
@@ -83344,8 +83387,8 @@
       <c r="P1566" s="2">
         <v>10.25</v>
       </c>
-      <c r="Q1566" s="2">
-        <v>20</v>
+      <c r="Q1566" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1567" spans="1:17" x14ac:dyDescent="0.25">
@@ -83397,8 +83440,8 @@
       <c r="P1567" s="2">
         <v>10.23</v>
       </c>
-      <c r="Q1567" s="2">
-        <v>20</v>
+      <c r="Q1567" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1568" spans="1:17" x14ac:dyDescent="0.25">
@@ -83450,8 +83493,8 @@
       <c r="P1568" s="2">
         <v>10.220000000000001</v>
       </c>
-      <c r="Q1568" s="2">
-        <v>20</v>
+      <c r="Q1568" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1569" spans="1:17" x14ac:dyDescent="0.25">
@@ -83503,8 +83546,8 @@
       <c r="P1569" s="2">
         <v>10.210000000000001</v>
       </c>
-      <c r="Q1569" s="2">
-        <v>20</v>
+      <c r="Q1569" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1570" spans="1:17" x14ac:dyDescent="0.25">
@@ -83556,8 +83599,8 @@
       <c r="P1570" s="2">
         <v>10.19</v>
       </c>
-      <c r="Q1570" s="2">
-        <v>20</v>
+      <c r="Q1570" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1571" spans="1:17" x14ac:dyDescent="0.25">
@@ -83609,8 +83652,8 @@
       <c r="P1571" s="2">
         <v>10.51</v>
       </c>
-      <c r="Q1571" s="2">
-        <v>20</v>
+      <c r="Q1571" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1572" spans="1:17" x14ac:dyDescent="0.25">
@@ -83662,8 +83705,8 @@
       <c r="P1572" s="2">
         <v>10.5</v>
       </c>
-      <c r="Q1572" s="2">
-        <v>20</v>
+      <c r="Q1572" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1573" spans="1:17" x14ac:dyDescent="0.25">
@@ -83715,8 +83758,8 @@
       <c r="P1573" s="2">
         <v>10.48</v>
       </c>
-      <c r="Q1573" s="2">
-        <v>20</v>
+      <c r="Q1573" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1574" spans="1:17" x14ac:dyDescent="0.25">
@@ -83768,8 +83811,8 @@
       <c r="P1574" s="2">
         <v>10.47</v>
       </c>
-      <c r="Q1574" s="2">
-        <v>20</v>
+      <c r="Q1574" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1575" spans="1:17" x14ac:dyDescent="0.25">
@@ -83821,8 +83864,8 @@
       <c r="P1575" s="2">
         <v>10.45</v>
       </c>
-      <c r="Q1575" s="2">
-        <v>20</v>
+      <c r="Q1575" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1576" spans="1:17" x14ac:dyDescent="0.25">
@@ -83874,8 +83917,8 @@
       <c r="P1576" s="2">
         <v>10.77</v>
       </c>
-      <c r="Q1576" s="2">
-        <v>20</v>
+      <c r="Q1576" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1577" spans="1:17" x14ac:dyDescent="0.25">
@@ -83927,8 +83970,8 @@
       <c r="P1577" s="2">
         <v>10.76</v>
       </c>
-      <c r="Q1577" s="2">
-        <v>20</v>
+      <c r="Q1577" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1578" spans="1:17" x14ac:dyDescent="0.25">
@@ -83980,8 +84023,8 @@
       <c r="P1578" s="2">
         <v>10.75</v>
       </c>
-      <c r="Q1578" s="2">
-        <v>20</v>
+      <c r="Q1578" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1579" spans="1:17" x14ac:dyDescent="0.25">
@@ -84033,8 +84076,8 @@
       <c r="P1579" s="2">
         <v>11.07</v>
       </c>
-      <c r="Q1579" s="2">
-        <v>20</v>
+      <c r="Q1579" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1580" spans="1:17" x14ac:dyDescent="0.25">
@@ -84086,8 +84129,8 @@
       <c r="P1580" s="2">
         <v>11.05</v>
       </c>
-      <c r="Q1580" s="2">
-        <v>20</v>
+      <c r="Q1580" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="1581" spans="1:17" x14ac:dyDescent="0.25">
@@ -84139,8 +84182,8 @@
       <c r="P1581" s="2">
         <v>0</v>
       </c>
-      <c r="Q1581" s="2">
-        <v>21</v>
+      <c r="Q1581" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1582" spans="1:17" x14ac:dyDescent="0.25">
@@ -84192,8 +84235,8 @@
       <c r="P1582" s="2">
         <v>0</v>
       </c>
-      <c r="Q1582" s="2">
-        <v>21</v>
+      <c r="Q1582" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1583" spans="1:17" x14ac:dyDescent="0.25">
@@ -84245,8 +84288,8 @@
       <c r="P1583" s="2">
         <v>0</v>
       </c>
-      <c r="Q1583" s="2">
-        <v>21</v>
+      <c r="Q1583" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1584" spans="1:17" x14ac:dyDescent="0.25">
@@ -84298,8 +84341,8 @@
       <c r="P1584" s="2">
         <v>0</v>
       </c>
-      <c r="Q1584" s="2">
-        <v>21</v>
+      <c r="Q1584" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1585" spans="1:17" x14ac:dyDescent="0.25">
@@ -84351,8 +84394,8 @@
       <c r="P1585" s="2">
         <v>0</v>
       </c>
-      <c r="Q1585" s="2">
-        <v>21</v>
+      <c r="Q1585" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1586" spans="1:17" x14ac:dyDescent="0.25">
@@ -84404,8 +84447,8 @@
       <c r="P1586" s="2">
         <v>0</v>
       </c>
-      <c r="Q1586" s="2">
-        <v>21</v>
+      <c r="Q1586" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1587" spans="1:17" x14ac:dyDescent="0.25">
@@ -84457,8 +84500,8 @@
       <c r="P1587" s="2">
         <v>0</v>
       </c>
-      <c r="Q1587" s="2">
-        <v>21</v>
+      <c r="Q1587" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1588" spans="1:17" x14ac:dyDescent="0.25">
@@ -84510,8 +84553,8 @@
       <c r="P1588" s="2">
         <v>0</v>
       </c>
-      <c r="Q1588" s="2">
-        <v>21</v>
+      <c r="Q1588" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1589" spans="1:17" x14ac:dyDescent="0.25">
@@ -84563,8 +84606,8 @@
       <c r="P1589" s="2">
         <v>0</v>
       </c>
-      <c r="Q1589" s="2">
-        <v>21</v>
+      <c r="Q1589" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1590" spans="1:17" x14ac:dyDescent="0.25">
@@ -84616,8 +84659,8 @@
       <c r="P1590" s="2">
         <v>0</v>
       </c>
-      <c r="Q1590" s="2">
-        <v>21</v>
+      <c r="Q1590" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1591" spans="1:17" x14ac:dyDescent="0.25">
@@ -84669,8 +84712,8 @@
       <c r="P1591" s="2">
         <v>0</v>
       </c>
-      <c r="Q1591" s="2">
-        <v>21</v>
+      <c r="Q1591" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1592" spans="1:17" x14ac:dyDescent="0.25">
@@ -84722,8 +84765,8 @@
       <c r="P1592" s="2">
         <v>0</v>
       </c>
-      <c r="Q1592" s="2">
-        <v>21</v>
+      <c r="Q1592" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1593" spans="1:17" x14ac:dyDescent="0.25">
@@ -84775,8 +84818,8 @@
       <c r="P1593" s="2">
         <v>0</v>
       </c>
-      <c r="Q1593" s="2">
-        <v>21</v>
+      <c r="Q1593" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1594" spans="1:17" x14ac:dyDescent="0.25">
@@ -84828,8 +84871,8 @@
       <c r="P1594" s="2">
         <v>0</v>
       </c>
-      <c r="Q1594" s="2">
-        <v>21</v>
+      <c r="Q1594" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1595" spans="1:17" x14ac:dyDescent="0.25">
@@ -84881,8 +84924,8 @@
       <c r="P1595" s="2">
         <v>0</v>
       </c>
-      <c r="Q1595" s="2">
-        <v>21</v>
+      <c r="Q1595" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1596" spans="1:17" x14ac:dyDescent="0.25">
@@ -84934,8 +84977,8 @@
       <c r="P1596" s="2">
         <v>0</v>
       </c>
-      <c r="Q1596" s="2">
-        <v>21</v>
+      <c r="Q1596" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1597" spans="1:17" x14ac:dyDescent="0.25">
@@ -84987,8 +85030,8 @@
       <c r="P1597" s="2">
         <v>0</v>
       </c>
-      <c r="Q1597" s="2">
-        <v>21</v>
+      <c r="Q1597" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1598" spans="1:17" x14ac:dyDescent="0.25">
@@ -85040,8 +85083,8 @@
       <c r="P1598" s="2">
         <v>0</v>
       </c>
-      <c r="Q1598" s="2">
-        <v>21</v>
+      <c r="Q1598" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1599" spans="1:17" x14ac:dyDescent="0.25">
@@ -85093,8 +85136,8 @@
       <c r="P1599" s="2">
         <v>0</v>
       </c>
-      <c r="Q1599" s="2">
-        <v>21</v>
+      <c r="Q1599" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="1600" spans="1:17" x14ac:dyDescent="0.25">
@@ -85146,8 +85189,8 @@
       <c r="P1600" s="2">
         <v>0</v>
       </c>
-      <c r="Q1600" s="2">
-        <v>21</v>
+      <c r="Q1600" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
